--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/ILLINOIS_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/ILLINOIS_2024.xlsx
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C226">
@@ -6637,7 +6637,7 @@
         <v>61</v>
       </c>
       <c r="D349">
-        <v>0.0009202685373759999</v>
+        <v>0.0009202685373760001</v>
       </c>
     </row>
     <row r="350">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C384">
@@ -7573,7 +7573,7 @@
         <v>61</v>
       </c>
       <c r="D401">
-        <v>0.0009202685373759999</v>
+        <v>0.0009202685373760001</v>
       </c>
     </row>
     <row r="402">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Huehuetl</t>
+          <t>Huehuetla</t>
         </is>
       </c>
       <c r="C524">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C527">
@@ -21865,7 +21865,7 @@
         <v>61</v>
       </c>
       <c r="D1195">
-        <v>0.0009202685373759999</v>
+        <v>0.0009202685373760001</v>
       </c>
     </row>
     <row r="1196">
@@ -23827,7 +23827,7 @@
         <v>61</v>
       </c>
       <c r="D1304">
-        <v>0.0009202685373759999</v>
+        <v>0.0009202685373760001</v>
       </c>
     </row>
     <row r="1305">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1540">
@@ -28237,7 +28237,7 @@
         <v>61</v>
       </c>
       <c r="D1549">
-        <v>0.0009202685373759999</v>
+        <v>0.0009202685373760001</v>
       </c>
     </row>
     <row r="1550">
